--- a/proposal/创智汇30场-双会资源导入摘要.xlsx
+++ b/proposal/创智汇30场-双会资源导入摘要.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>适度承兑约50%，不做100%承诺</t>
+          <t>≤30%</t>
         </is>
       </c>
     </row>
